--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_pet.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_pet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_pet" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="126">
   <si>
     <t>召唤兽id</t>
   </si>
@@ -223,286 +223,304 @@
     <t>27001</t>
   </si>
   <si>
+    <t>207011#3600|206011#3600|201021#3600|201011#3600</t>
+  </si>
+  <si>
+    <t>2#1303001#2</t>
+  </si>
+  <si>
+    <t>207011#4250|206011#4250|201021#4250|201011#4250</t>
+  </si>
+  <si>
+    <t>2#1303001#3</t>
+  </si>
+  <si>
+    <t>207011#5000|206011#5000|201021#5000|201011#5000</t>
+  </si>
+  <si>
+    <t>2#1303001#4</t>
+  </si>
+  <si>
+    <t>27002</t>
+  </si>
+  <si>
+    <t>130000411#1</t>
+  </si>
+  <si>
+    <t>2#1303001#5</t>
+  </si>
+  <si>
+    <t>27003</t>
+  </si>
+  <si>
+    <t>130000412#1</t>
+  </si>
+  <si>
+    <t>召唤石巨人</t>
+  </si>
+  <si>
+    <t>2#1303002#1</t>
+  </si>
+  <si>
+    <t>27004</t>
+  </si>
+  <si>
+    <t>207011#4300|206011#4300|201021#4300|201011#4300</t>
+  </si>
+  <si>
+    <t>2#1303002#2</t>
+  </si>
+  <si>
+    <t>207011#5100|206011#5100|201021#5100|201011#5100</t>
+  </si>
+  <si>
+    <t>2#1303002#3</t>
+  </si>
+  <si>
+    <t>207011#6000|206011#6000|201021#6000|201011#6000</t>
+  </si>
+  <si>
+    <t>2#1303002#4</t>
+  </si>
+  <si>
+    <t>27005</t>
+  </si>
+  <si>
+    <t>2#1303002#5</t>
+  </si>
+  <si>
+    <t>27006</t>
+  </si>
+  <si>
+    <t>召唤暗杀者</t>
+  </si>
+  <si>
+    <t>2#1303003#1</t>
+  </si>
+  <si>
+    <t>2#1303003#2</t>
+  </si>
+  <si>
+    <t>207011#5950|206011#5950|201021#5950|201011#5950</t>
+  </si>
+  <si>
+    <t>2#1303003#3</t>
+  </si>
+  <si>
+    <t>207011#7000|206011#7000|201021#7000|201011#7000</t>
+  </si>
+  <si>
+    <t>2#1303003#4</t>
+  </si>
+  <si>
+    <t>27008</t>
+  </si>
+  <si>
+    <t>2#1303003#5</t>
+  </si>
+  <si>
+    <t>27009</t>
+  </si>
+  <si>
+    <t>召唤雪人王</t>
+  </si>
+  <si>
+    <t>2#1303004#1</t>
+  </si>
+  <si>
+    <t>27010</t>
+  </si>
+  <si>
+    <t>207011#5700|206011#5700|201021#5700|201011#5700</t>
+  </si>
+  <si>
+    <t>2#1303004#2</t>
+  </si>
+  <si>
+    <t>207011#6800|206011#6800|201021#6800|201011#6800</t>
+  </si>
+  <si>
+    <t>2#1303004#3</t>
+  </si>
+  <si>
+    <t>207011#8000|206011#8000|201021#8000|201011#8000</t>
+  </si>
+  <si>
+    <t>2#1303004#4</t>
+  </si>
+  <si>
+    <t>27011</t>
+  </si>
+  <si>
+    <t>2#1303004#5</t>
+  </si>
+  <si>
+    <t>27012</t>
+  </si>
+  <si>
+    <t>召唤黑骑士</t>
+  </si>
+  <si>
+    <t>2#1303005#1</t>
+  </si>
+  <si>
+    <t>27013</t>
+  </si>
+  <si>
+    <t>207011#6500|206011#6500|201021#6500|201011#6500</t>
+  </si>
+  <si>
+    <t>2#1303005#2</t>
+  </si>
+  <si>
+    <t>207011#7650|206011#7650|201021#7650|201011#7650</t>
+  </si>
+  <si>
+    <t>2#1303005#3</t>
+  </si>
+  <si>
+    <t>207011#9000|206011#9000|201021#9000|201011#9000</t>
+  </si>
+  <si>
+    <t>2#1303005#4</t>
+  </si>
+  <si>
+    <t>27014</t>
+  </si>
+  <si>
+    <t>2#1303005#5</t>
+  </si>
+  <si>
+    <t>27015</t>
+  </si>
+  <si>
+    <t>召唤守护兽巴里</t>
+  </si>
+  <si>
+    <t>2#1303006#1</t>
+  </si>
+  <si>
+    <t>27019</t>
+  </si>
+  <si>
+    <t>207011#7200|206011#7200|201021#7200|201011#7200</t>
+  </si>
+  <si>
+    <t>2#1303006#2</t>
+  </si>
+  <si>
+    <t>207011#8500|206011#8500|201021#8500|201011#8500</t>
+  </si>
+  <si>
+    <t>2#1303006#3</t>
+  </si>
+  <si>
+    <t>207011#10000|206011#10000|201021#10000|201011#10000</t>
+  </si>
+  <si>
+    <t>2#1303006#4</t>
+  </si>
+  <si>
+    <t>27020</t>
+  </si>
+  <si>
+    <t>2#1303006#5</t>
+  </si>
+  <si>
+    <t>27021</t>
+  </si>
+  <si>
+    <t>召唤黄金斗士</t>
+  </si>
+  <si>
+    <t>2#1303007#1</t>
+  </si>
+  <si>
+    <t>27016</t>
+  </si>
+  <si>
+    <t>207011#9300|206011#9300|201021#9300|201011#9300</t>
+  </si>
+  <si>
+    <t>2#1303007#2</t>
+  </si>
+  <si>
+    <t>207011#11050|206011#11050|201021#11050|201011#11050</t>
+  </si>
+  <si>
+    <t>2#1303007#3</t>
+  </si>
+  <si>
+    <t>207011#13000|206011#13000|201021#13000|201011#13000</t>
+  </si>
+  <si>
+    <t>2#1303007#4</t>
+  </si>
+  <si>
+    <t>27017</t>
+  </si>
+  <si>
+    <t>2#1303007#5</t>
+  </si>
+  <si>
+    <t>27018</t>
+  </si>
+  <si>
+    <t>天鹰</t>
+  </si>
+  <si>
+    <t>1#21800001</t>
+  </si>
+  <si>
+    <t>召唤兽名称</t>
+  </si>
+  <si>
+    <t>1级系数</t>
+  </si>
+  <si>
+    <t>2级系数</t>
+  </si>
+  <si>
+    <t>3级系数</t>
+  </si>
+  <si>
+    <t>4级系数</t>
+  </si>
+  <si>
+    <t>5级系数</t>
+  </si>
+  <si>
+    <t>召唤暗黑骑士</t>
+  </si>
+  <si>
+    <t>生命值属性ID</t>
+  </si>
+  <si>
+    <t>防御力属性ID</t>
+  </si>
+  <si>
+    <t>最下攻击属性ID</t>
+  </si>
+  <si>
+    <t>最大攻击属性ID</t>
+  </si>
+  <si>
     <t>207011#3500|206011#3500|201021#3500|201011#3500</t>
   </si>
   <si>
-    <t>2#1303001#2</t>
-  </si>
-  <si>
-    <t>207011#4250|206011#4250|201021#4250|201011#4250</t>
-  </si>
-  <si>
-    <t>2#1303001#3</t>
-  </si>
-  <si>
-    <t>207011#5000|206011#5000|201021#5000|201011#5000</t>
-  </si>
-  <si>
-    <t>2#1303001#4</t>
-  </si>
-  <si>
-    <t>27002</t>
-  </si>
-  <si>
-    <t>130000411#1</t>
-  </si>
-  <si>
-    <t>2#1303001#5</t>
-  </si>
-  <si>
-    <t>27003</t>
-  </si>
-  <si>
-    <t>130000412#1</t>
-  </si>
-  <si>
-    <t>召唤石巨人</t>
-  </si>
-  <si>
-    <t>2#1303002#1</t>
-  </si>
-  <si>
-    <t>27004</t>
-  </si>
-  <si>
     <t>207011#4200|206011#4200|201021#4200|201011#4200</t>
   </si>
   <si>
-    <t>2#1303002#2</t>
-  </si>
-  <si>
-    <t>207011#5100|206011#5100|201021#5100|201011#5100</t>
-  </si>
-  <si>
-    <t>2#1303002#3</t>
-  </si>
-  <si>
-    <t>207011#6000|206011#6000|201021#6000|201011#6000</t>
-  </si>
-  <si>
-    <t>2#1303002#4</t>
-  </si>
-  <si>
-    <t>27005</t>
-  </si>
-  <si>
-    <t>2#1303002#5</t>
-  </si>
-  <si>
-    <t>27006</t>
-  </si>
-  <si>
-    <t>召唤暗杀者</t>
-  </si>
-  <si>
-    <t>2#1303003#1</t>
-  </si>
-  <si>
     <t>207011#4900|206011#4900|201021#4900|201011#4900</t>
   </si>
   <si>
-    <t>2#1303003#2</t>
-  </si>
-  <si>
-    <t>207011#5950|206011#5950|201021#5950|201011#5950</t>
-  </si>
-  <si>
-    <t>2#1303003#3</t>
-  </si>
-  <si>
-    <t>207011#7000|206011#7000|201021#7000|201011#7000</t>
-  </si>
-  <si>
-    <t>2#1303003#4</t>
-  </si>
-  <si>
-    <t>27008</t>
-  </si>
-  <si>
-    <t>2#1303003#5</t>
-  </si>
-  <si>
-    <t>27009</t>
-  </si>
-  <si>
-    <t>召唤雪人王</t>
-  </si>
-  <si>
-    <t>2#1303004#1</t>
-  </si>
-  <si>
-    <t>27010</t>
-  </si>
-  <si>
     <t>207011#5600|206011#5600|201021#5600|201011#5600</t>
   </si>
   <si>
-    <t>2#1303004#2</t>
-  </si>
-  <si>
-    <t>207011#6800|206011#6800|201021#6800|201011#6800</t>
-  </si>
-  <si>
-    <t>2#1303004#3</t>
-  </si>
-  <si>
-    <t>207011#8000|206011#8000|201021#8000|201011#8000</t>
-  </si>
-  <si>
-    <t>2#1303004#4</t>
-  </si>
-  <si>
-    <t>27011</t>
-  </si>
-  <si>
-    <t>2#1303004#5</t>
-  </si>
-  <si>
-    <t>27012</t>
-  </si>
-  <si>
-    <t>召唤黑骑士</t>
-  </si>
-  <si>
-    <t>2#1303005#1</t>
-  </si>
-  <si>
-    <t>27013</t>
-  </si>
-  <si>
     <t>207011#6300|206011#6300|201021#6300|201011#6300</t>
   </si>
   <si>
-    <t>2#1303005#2</t>
-  </si>
-  <si>
-    <t>207011#7650|206011#7650|201021#7650|201011#7650</t>
-  </si>
-  <si>
-    <t>2#1303005#3</t>
-  </si>
-  <si>
-    <t>207011#9000|206011#9000|201021#9000|201011#9000</t>
-  </si>
-  <si>
-    <t>2#1303005#4</t>
-  </si>
-  <si>
-    <t>27014</t>
-  </si>
-  <si>
-    <t>2#1303005#5</t>
-  </si>
-  <si>
-    <t>27015</t>
-  </si>
-  <si>
-    <t>召唤守护兽巴里</t>
-  </si>
-  <si>
-    <t>2#1303006#1</t>
-  </si>
-  <si>
-    <t>27019</t>
-  </si>
-  <si>
-    <t>2#1303006#2</t>
-  </si>
-  <si>
-    <t>207011#8500|206011#8500|201021#8500|201011#8500</t>
-  </si>
-  <si>
-    <t>2#1303006#3</t>
-  </si>
-  <si>
-    <t>207011#10000|206011#10000|201021#10000|201011#10000</t>
-  </si>
-  <si>
-    <t>2#1303006#4</t>
-  </si>
-  <si>
-    <t>27020</t>
-  </si>
-  <si>
-    <t>2#1303006#5</t>
-  </si>
-  <si>
-    <t>27021</t>
-  </si>
-  <si>
-    <t>召唤黄金斗士</t>
-  </si>
-  <si>
-    <t>2#1303007#1</t>
-  </si>
-  <si>
-    <t>27016</t>
-  </si>
-  <si>
     <t>207011#9100|206011#9100|201021#9100|201011#9100</t>
-  </si>
-  <si>
-    <t>2#1303007#2</t>
-  </si>
-  <si>
-    <t>207011#11050|206011#11050|201021#11050|201011#11050</t>
-  </si>
-  <si>
-    <t>2#1303007#3</t>
-  </si>
-  <si>
-    <t>207011#13000|206011#13000|201021#13000|201011#13000</t>
-  </si>
-  <si>
-    <t>2#1303007#4</t>
-  </si>
-  <si>
-    <t>27017</t>
-  </si>
-  <si>
-    <t>2#1303007#5</t>
-  </si>
-  <si>
-    <t>27018</t>
-  </si>
-  <si>
-    <t>天鹰</t>
-  </si>
-  <si>
-    <t>1#21800001</t>
-  </si>
-  <si>
-    <t>召唤兽名称</t>
-  </si>
-  <si>
-    <t>1级系数</t>
-  </si>
-  <si>
-    <t>2级系数</t>
-  </si>
-  <si>
-    <t>3级系数</t>
-  </si>
-  <si>
-    <t>4级系数</t>
-  </si>
-  <si>
-    <t>5级系数</t>
-  </si>
-  <si>
-    <t>召唤暗黑骑士</t>
-  </si>
-  <si>
-    <t>生命值属性ID</t>
-  </si>
-  <si>
-    <t>防御力属性ID</t>
-  </si>
-  <si>
-    <t>最下攻击属性ID</t>
-  </si>
-  <si>
-    <t>最大攻击属性ID</t>
   </si>
 </sst>
 </file>
@@ -1995,7 +2013,7 @@
         <v>27007</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2006,13 +2024,13 @@
         <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" s="5">
         <v>27007</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2023,13 +2041,13 @@
         <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" s="5">
         <v>27007</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2040,13 +2058,13 @@
         <v>49</v>
       </c>
       <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s">
         <v>33</v>
@@ -2060,13 +2078,13 @@
         <v>49</v>
       </c>
       <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s">
         <v>36</v>
@@ -2077,16 +2095,16 @@
         <v>130300401</v>
       </c>
       <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
         <v>60</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" t="s">
         <v>62</v>
-      </c>
-      <c r="E20" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:6">
@@ -2094,16 +2112,16 @@
         <v>130300402</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" t="s">
         <v>64</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:6">
@@ -2111,16 +2129,16 @@
         <v>130300403</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" t="s">
         <v>66</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:6">
@@ -2128,16 +2146,16 @@
         <v>130300404</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F23" t="s">
         <v>33</v>
@@ -2148,16 +2166,16 @@
         <v>130300405</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F24" t="s">
         <v>36</v>
@@ -2168,16 +2186,16 @@
         <v>130300501</v>
       </c>
       <c r="B25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" t="s">
         <v>72</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" t="s">
         <v>74</v>
-      </c>
-      <c r="E25" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2185,16 +2203,16 @@
         <v>130300502</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" t="s">
         <v>76</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2202,16 +2220,16 @@
         <v>130300503</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" t="s">
         <v>78</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2219,16 +2237,16 @@
         <v>130300504</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="E28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F28" t="s">
         <v>33</v>
@@ -2239,16 +2257,16 @@
         <v>130300505</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="E29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F29" t="s">
         <v>36</v>
@@ -2259,16 +2277,16 @@
         <v>130300601</v>
       </c>
       <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s">
         <v>84</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" t="s">
         <v>86</v>
-      </c>
-      <c r="E30" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2276,13 +2294,13 @@
         <v>130300602</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
         <v>87</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s">
         <v>88</v>
@@ -2293,13 +2311,13 @@
         <v>130300603</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C32" t="s">
         <v>89</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E32" t="s">
         <v>90</v>
@@ -2310,7 +2328,7 @@
         <v>130300604</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s">
         <v>91</v>
@@ -2330,7 +2348,7 @@
         <v>130300605</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
         <v>93</v>
@@ -2614,7 +2632,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5">
         <v>5600</v>
@@ -2654,7 +2672,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7">
         <v>7000</v>
@@ -2732,7 +2750,7 @@
         <v>3500</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2877,7 +2895,7 @@
         <v>4200</v>
       </c>
       <c r="I17" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -3022,7 +3040,7 @@
         <v>4900</v>
       </c>
       <c r="I22" t="s">
-        <v>51</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -3051,7 +3069,7 @@
         <v>5950</v>
       </c>
       <c r="I23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3080,7 +3098,7 @@
         <v>7000</v>
       </c>
       <c r="I24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3109,7 +3127,7 @@
         <v>7000</v>
       </c>
       <c r="I25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3138,7 +3156,7 @@
         <v>7000</v>
       </c>
       <c r="I26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3167,7 +3185,7 @@
         <v>5600</v>
       </c>
       <c r="I27" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3196,7 +3214,7 @@
         <v>6800</v>
       </c>
       <c r="I28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3225,7 +3243,7 @@
         <v>8000</v>
       </c>
       <c r="I29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3254,7 +3272,7 @@
         <v>8000</v>
       </c>
       <c r="I30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3283,7 +3301,7 @@
         <v>8000</v>
       </c>
       <c r="I31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -3312,7 +3330,7 @@
         <v>6300</v>
       </c>
       <c r="I32" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -3341,7 +3359,7 @@
         <v>7650</v>
       </c>
       <c r="I33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -3370,7 +3388,7 @@
         <v>9000</v>
       </c>
       <c r="I34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -3399,7 +3417,7 @@
         <v>9000</v>
       </c>
       <c r="I35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -3428,7 +3446,7 @@
         <v>9000</v>
       </c>
       <c r="I36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -3457,7 +3475,7 @@
         <v>7000</v>
       </c>
       <c r="I37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -3602,7 +3620,7 @@
         <v>9100</v>
       </c>
       <c r="I42" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:9">
